--- a/data/trans_camb/IP16A10-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Habitat-trans_camb.xlsx
@@ -636,27 +636,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 12,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 6,71</t>
+          <t>-6,97; 6,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 0,0</t>
+          <t>-12,22; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,29</t>
+          <t>-3,2; 3,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,97</t>
+          <t>-2,45; 3,85</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 4,47</t>
+          <t>-11,24; 4,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,94; -2,62</t>
+          <t>-15,2; -2,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,01</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,02</t>
+          <t>-4,2; 3,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 228,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,58; 322,46</t>
+          <t>-84,86; 271,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,35; -4,11</t>
+          <t>-25,75; -3,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,82; -4,04</t>
+          <t>-26,87; -4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 5,06</t>
+          <t>-8,69; 4,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 14,72</t>
+          <t>-5,44; 11,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; -0,53</t>
+          <t>-12,7; -1,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 2,17</t>
+          <t>-11,53; 2,14</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,98</t>
+          <t>-100,0; -4,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -5,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-94,35; 11,8</t>
+          <t>-93,57; 9,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 80,73</t>
+          <t>-90,1; 70,69</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 0,0</t>
+          <t>-10,62; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 0,0</t>
+          <t>-8,83; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 0,0</t>
+          <t>-5,31; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 0,0</t>
+          <t>-4,96; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -0,62</t>
+          <t>-7,56; -0,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -1,65</t>
+          <t>-7,94; -1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,8</t>
+          <t>-2,17; 3,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,79</t>
+          <t>-2,93; 1,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,28</t>
+          <t>-3,86; 0,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,46</t>
+          <t>-4,49; -0,49</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,2; 0,29</t>
+          <t>-91,65; -6,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -26,48</t>
+          <t>-95,06; -31,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,32; 420,35</t>
+          <t>-71,11; 662,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,16; 19,48</t>
+          <t>-77,19; 16,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,83; -7,41</t>
+          <t>-88,89; -7,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Habitat-trans_camb.xlsx
@@ -636,27 +636,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,18</t>
+          <t>0,0; 12,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 6,56</t>
+          <t>-5,53; 6,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 0,0</t>
+          <t>-11,74; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,25</t>
+          <t>-2,65; 3,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,85</t>
+          <t>-2,43; 3,89</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 4,75</t>
+          <t>-10,95; 4,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -2,67</t>
+          <t>-15,42; -2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,02</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,8</t>
+          <t>-4,05; 4,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; -1,34</t>
+          <t>-8,24; -1,38</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 228,25</t>
+          <t>-100,0; 351,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,86; 271,59</t>
+          <t>-81,34; 334,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,75; -3,56</t>
+          <t>-25,69; -3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,87; -4,5</t>
+          <t>-28,03; -4,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 4,57</t>
+          <t>-8,73; 4,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 11,49</t>
+          <t>-5,51; 12,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,7; -1,01</t>
+          <t>-13,26; -0,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 2,14</t>
+          <t>-11,35; 1,54</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -5,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-93,57; 9,98</t>
+          <t>-93,49; 11,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,1; 70,69</t>
+          <t>-89,41; 81,41</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 0,0</t>
+          <t>-8,98; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 0,0</t>
+          <t>-8,1; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,0</t>
+          <t>-5,32; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,0</t>
+          <t>-5,9; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,71</t>
+          <t>-7,67; -0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -1,54</t>
+          <t>-8,47; -1,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,12</t>
+          <t>-2,55; 2,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,82</t>
+          <t>-2,94; 1,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,2</t>
+          <t>-3,74; 0,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,49</t>
+          <t>-4,26; -0,47</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-91,65; -6,11</t>
+          <t>-90,95; -11,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-95,06; -31,45</t>
+          <t>-100,0; -29,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 662,14</t>
+          <t>-80,52; 446,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 320,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,19; 16,97</t>
+          <t>-76,9; 16,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,89; -7,86</t>
+          <t>-88,33; -8,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Habitat-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,97</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3,58</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,51; 6,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>-11,38; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 6,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 0,0</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,71</t>
+          <t>-2,53; 3,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,89</t>
+          <t>-2,54; 3,97</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>41,86%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-6,96</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 4,58</t>
+          <t>0,0; 9,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,42; -2,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>-10,73; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,94; -2,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 4,32</t>
+          <t>-4,43; 4,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -1,38</t>
+          <t>-7,88; -1,34</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-39,75%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 351,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 334,07</t>
+          <t>-82,58; 322,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-12,89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-13,68</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,69; -3,2</t>
+          <t>-8,29; 5,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-28,03; -4,29</t>
+          <t>-4,09; 14,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 4,59</t>
+          <t>-26,35; -4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 12,69</t>
+          <t>-26,82; -4,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,26; -0,2</t>
+          <t>-12,86; -0,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 1,54</t>
+          <t>-11,8; 2,17</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-24,14%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63,62%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-83,26%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-88,33%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-24,14%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63,62%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -22,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-93,49; 11,91</t>
+          <t>-94,35; 11,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,41; 81,41</t>
+          <t>-89,62; 80,73</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,95; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,97; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,0</t>
+          <t>-5,35; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,0</t>
+          <t>-6,47; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-3,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-4,34</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -0,85</t>
+          <t>-2,52; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -1,57</t>
+          <t>-3,25; 1,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,59</t>
+          <t>-7,41; -0,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,81</t>
+          <t>-8,43; -1,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,29</t>
+          <t>-3,68; 0,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -0,47</t>
+          <t>-4,32; -0,46</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-26,32%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-67,5%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-80,02%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-26,32%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,95; -11,08</t>
+          <t>-77,32; 420,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 446,25</t>
+          <t>-90,2; 0,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 320,71</t>
+          <t>-95,53; -26,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 16,56</t>
+          <t>-76,16; 19,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,33; -8,58</t>
+          <t>-87,83; -7,41</t>
         </is>
       </c>
     </row>
